--- a/comptes_modele.xlsx
+++ b/comptes_modele.xlsx
@@ -592,7 +592,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>urgences_demo_annecy</t>
+          <t>urgences_demo</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -602,17 +602,17 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Urgences Annecy</t>
+          <t>Urgences Hôpital 1</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>directeur</t>
+          <t>cellule_crise</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Site hospitalier principal Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -622,7 +622,7 @@
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>urgences.annecy@chag.fr</t>
+          <t>urgences.h1@example.org</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -639,7 +639,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>reanimation_demo_annecy</t>
+          <t>reanimation_demo</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -649,17 +649,17 @@
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>Réanimation Annecy</t>
+          <t>Réanimation Hôpital 1</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>directeur</t>
+          <t>cellule_crise</t>
         </is>
       </c>
       <c r="E3" s="3" t="inlineStr">
         <is>
-          <t>Site hospitalier principal Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
@@ -669,7 +669,7 @@
       </c>
       <c r="G3" s="3" t="inlineStr">
         <is>
-          <t>rea.annecy@chag.fr</t>
+          <t>rea.h1@example.org</t>
         </is>
       </c>
       <c r="H3" s="3" t="inlineStr">
@@ -686,7 +686,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>dsi_demo_chag</t>
+          <t>dsi_demo</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -701,12 +701,12 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>directeur</t>
+          <t>cellule_crise</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Site hospitalier principal Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -716,7 +716,7 @@
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>dsi@chag.fr</t>
+          <t>dsi@example.org</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -733,7 +733,7 @@
     <row r="5">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>direction_demo_chag</t>
+          <t>direction_demo</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>Site hospitalier principal Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
@@ -763,7 +763,7 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>direction@chag.fr</t>
+          <t>direction@example.org</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>observateur</t>
+          <t>cellule_crise</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr"/>
@@ -834,7 +834,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>observateur</t>
+          <t>cellule_crise</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr"/>
@@ -855,6 +855,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
@@ -933,114 +934,130 @@
     <row r="2">
       <c r="A2" s="8" t="inlineStr">
         <is>
-          <t>Site hospitalier principal Annecy</t>
+          <t>Hôpital 1</t>
         </is>
       </c>
       <c r="B2" s="8" t="inlineStr">
         <is>
-          <t>1 Avenue de l'Hôpital, 74370 Épagny</t>
+          <t>1 rue de l'Hôpital, 00000 Ville Principale</t>
         </is>
       </c>
       <c r="C2" s="8" t="inlineStr">
         <is>
-          <t>45.9262</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="D2" s="8" t="inlineStr">
         <is>
-          <t>6.1042</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="E2" s="8" t="inlineStr">
         <is>
-          <t>04 50 63 65 65</t>
+          <t>0X XX XX XX 00</t>
         </is>
       </c>
       <c r="F2" s="8" t="inlineStr">
         <is>
-          <t>740000001</t>
+          <t>000000001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="8" t="inlineStr">
         <is>
-          <t>Hôpital Saint-Julien</t>
+          <t>Hôpital 2</t>
         </is>
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>1 Rue Amédée VIII, 74160 Saint-Julien</t>
+          <t>1 avenue Centrale, 00000 Ville Secondaire</t>
         </is>
       </c>
       <c r="C3" s="8" t="inlineStr">
         <is>
-          <t>46.1439</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="D3" s="8" t="inlineStr">
         <is>
-          <t>6.0858</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="E3" s="8" t="inlineStr">
         <is>
-          <t>04 50 49 60 00</t>
+          <t>0X XX XX XX 01</t>
         </is>
       </c>
       <c r="F3" s="8" t="inlineStr">
         <is>
-          <t>740000002</t>
+          <t>000000002</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="8" t="inlineStr">
         <is>
-          <t>CH du Pays de Gex</t>
+          <t>Hôpital 3</t>
         </is>
       </c>
       <c r="B4" s="8" t="inlineStr">
         <is>
-          <t>160 Rue Marc Panissod, 01170 Gex</t>
+          <t>1 place du Centre, 00000 Ville Tertiaire</t>
         </is>
       </c>
       <c r="C4" s="8" t="inlineStr">
         <is>
-          <t>46.3351</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="D4" s="8" t="inlineStr">
         <is>
-          <t>6.0594</t>
-        </is>
-      </c>
-      <c r="E4" s="8" t="inlineStr"/>
-      <c r="F4" s="8" t="inlineStr"/>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="E4" s="8" t="inlineStr">
+        <is>
+          <t>0X XX XX XX 02</t>
+        </is>
+      </c>
+      <c r="F4" s="8" t="inlineStr">
+        <is>
+          <t>000000003</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t>CH de Rumilly</t>
+          <t>Hôpital 4</t>
         </is>
       </c>
       <c r="B5" s="8" t="inlineStr">
         <is>
-          <t>1 Rue du Docteur Gallet, 74150 Rumilly</t>
+          <t>1 chemin du Site 4, 00000 Ville Quaternaire</t>
         </is>
       </c>
       <c r="C5" s="8" t="inlineStr">
         <is>
-          <t>45.8655</t>
+          <t>0.0000</t>
         </is>
       </c>
       <c r="D5" s="8" t="inlineStr">
         <is>
-          <t>5.9402</t>
-        </is>
-      </c>
-      <c r="E5" s="8" t="inlineStr"/>
-      <c r="F5" s="8" t="inlineStr"/>
+          <t>0.0000</t>
+        </is>
+      </c>
+      <c r="E5" s="8" t="inlineStr">
+        <is>
+          <t>0X XX XX XX 03</t>
+        </is>
+      </c>
+      <c r="F5" s="8" t="inlineStr">
+        <is>
+          <t>000000004</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
